--- a/research/traditional_assets/database/data/peru/peru_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_telecom_services.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0575</v>
+        <v>-0.0293</v>
       </c>
       <c r="G2">
-        <v>0.1103047024952015</v>
+        <v>0.1041413583655439</v>
       </c>
       <c r="H2">
-        <v>0.1103047024952015</v>
+        <v>0.1041413583655439</v>
       </c>
       <c r="I2">
-        <v>-0.08236202627401205</v>
+        <v>-0.001909485093240669</v>
       </c>
       <c r="J2">
-        <v>-0.08236202627401205</v>
+        <v>-0.001909485093240669</v>
       </c>
       <c r="K2">
-        <v>-294.2</v>
+        <v>-281.4</v>
       </c>
       <c r="L2">
-        <v>-0.1764635316698656</v>
+        <v>-0.1553837658752071</v>
       </c>
       <c r="M2">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="N2">
-        <v>5.709935287400076e-06</v>
+        <v>5.060728744939271e-06</v>
       </c>
       <c r="O2">
-        <v>-1.019714479945615e-05</v>
+        <v>-7.107320540156362e-06</v>
       </c>
       <c r="P2">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="Q2">
-        <v>5.709935287400076e-06</v>
+        <v>5.060728744939271e-06</v>
       </c>
       <c r="R2">
-        <v>-1.019714479945615e-05</v>
+        <v>-7.107320540156362e-06</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>231.3</v>
+        <v>119.8</v>
       </c>
       <c r="V2">
-        <v>0.4402360106585459</v>
+        <v>0.3031376518218624</v>
       </c>
       <c r="W2">
-        <v>-0.2489001692047377</v>
+        <v>-0.3801161691206268</v>
       </c>
       <c r="X2">
-        <v>0.09162112116895683</v>
+        <v>0.1735969306055751</v>
       </c>
       <c r="Y2">
-        <v>-0.3405212903736946</v>
+        <v>-0.5537130997262019</v>
       </c>
       <c r="Z2">
-        <v>0.8094108179971019</v>
+        <v>1.453753942750733</v>
       </c>
       <c r="AA2">
-        <v>-0.0666647150583469</v>
+        <v>-0.002775921482922372</v>
       </c>
       <c r="AB2">
-        <v>0.05180647383091749</v>
+        <v>0.08732653559018479</v>
       </c>
       <c r="AC2">
-        <v>-0.1184711888892644</v>
+        <v>-0.09010245707310716</v>
       </c>
       <c r="AD2">
-        <v>1024.7</v>
+        <v>1056.2</v>
       </c>
       <c r="AE2">
-        <v>2.469851020164505</v>
+        <v>6.440387519294253</v>
       </c>
       <c r="AF2">
-        <v>1027.169851020165</v>
+        <v>1062.640387519294</v>
       </c>
       <c r="AG2">
-        <v>795.8698510201646</v>
+        <v>942.8403875192944</v>
       </c>
       <c r="AH2">
-        <v>0.6615933256369949</v>
+        <v>0.72891408182724</v>
       </c>
       <c r="AI2">
-        <v>0.5811526858165604</v>
+        <v>0.6859105895249972</v>
       </c>
       <c r="AJ2">
-        <v>0.6023522374370884</v>
+        <v>0.7046426971216507</v>
       </c>
       <c r="AK2">
-        <v>0.5180871441342443</v>
+        <v>0.6595870634070552</v>
       </c>
       <c r="AL2">
-        <v>63.9</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AM2">
-        <v>61.09</v>
+        <v>73.97999999999999</v>
       </c>
       <c r="AN2">
-        <v>10.0185764567853</v>
+        <v>4.115652885477147</v>
       </c>
       <c r="AO2">
-        <v>-2.181533646322379</v>
+        <v>-0.05377720870678618</v>
       </c>
       <c r="AP2">
-        <v>7.7812852074713</v>
+        <v>3.673928954211489</v>
       </c>
       <c r="AQ2">
-        <v>-2.281879194630873</v>
+        <v>-0.05677210056772101</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0575</v>
+        <v>-0.0293</v>
       </c>
       <c r="G3">
-        <v>0.1103047024952015</v>
+        <v>0.1041413583655439</v>
       </c>
       <c r="H3">
-        <v>0.1103047024952015</v>
+        <v>0.1041413583655439</v>
       </c>
       <c r="I3">
-        <v>-0.08236202627401205</v>
+        <v>-0.001909485093240669</v>
       </c>
       <c r="J3">
-        <v>-0.08236202627401205</v>
+        <v>-0.001909485093240669</v>
       </c>
       <c r="K3">
-        <v>-294.2</v>
+        <v>-281.4</v>
       </c>
       <c r="L3">
-        <v>-0.1764635316698656</v>
+        <v>-0.1553837658752071</v>
       </c>
       <c r="M3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="N3">
-        <v>5.709935287400076e-06</v>
+        <v>5.060728744939271e-06</v>
       </c>
       <c r="O3">
-        <v>-1.019714479945615e-05</v>
+        <v>-7.107320540156362e-06</v>
       </c>
       <c r="P3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="Q3">
-        <v>5.709935287400076e-06</v>
+        <v>5.060728744939271e-06</v>
       </c>
       <c r="R3">
-        <v>-1.019714479945615e-05</v>
+        <v>-7.107320540156362e-06</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>231.3</v>
+        <v>119.8</v>
       </c>
       <c r="V3">
-        <v>0.4402360106585459</v>
+        <v>0.3031376518218624</v>
       </c>
       <c r="W3">
-        <v>-0.2489001692047377</v>
+        <v>-0.3801161691206268</v>
       </c>
       <c r="X3">
-        <v>0.09162112116895683</v>
+        <v>0.1735969306055751</v>
       </c>
       <c r="Y3">
-        <v>-0.3405212903736946</v>
+        <v>-0.5537130997262019</v>
       </c>
       <c r="Z3">
-        <v>0.8094108179971019</v>
+        <v>1.453753942750733</v>
       </c>
       <c r="AA3">
-        <v>-0.0666647150583469</v>
+        <v>-0.002775921482922372</v>
       </c>
       <c r="AB3">
-        <v>0.05180647383091749</v>
+        <v>0.08732653559018479</v>
       </c>
       <c r="AC3">
-        <v>-0.1184711888892644</v>
+        <v>-0.09010245707310716</v>
       </c>
       <c r="AD3">
-        <v>1024.7</v>
+        <v>1056.2</v>
       </c>
       <c r="AE3">
-        <v>2.469851020164505</v>
+        <v>6.440387519294253</v>
       </c>
       <c r="AF3">
-        <v>1027.169851020165</v>
+        <v>1062.640387519294</v>
       </c>
       <c r="AG3">
-        <v>795.8698510201646</v>
+        <v>942.8403875192944</v>
       </c>
       <c r="AH3">
-        <v>0.6615933256369949</v>
+        <v>0.72891408182724</v>
       </c>
       <c r="AI3">
-        <v>0.5811526858165604</v>
+        <v>0.6859105895249972</v>
       </c>
       <c r="AJ3">
-        <v>0.6023522374370884</v>
+        <v>0.7046426971216507</v>
       </c>
       <c r="AK3">
-        <v>0.5180871441342443</v>
+        <v>0.6595870634070552</v>
       </c>
       <c r="AL3">
-        <v>63.9</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AM3">
-        <v>61.09</v>
+        <v>73.97999999999999</v>
       </c>
       <c r="AN3">
-        <v>10.0185764567853</v>
+        <v>4.115652885477147</v>
       </c>
       <c r="AO3">
-        <v>-2.181533646322379</v>
+        <v>-0.05377720870678618</v>
       </c>
       <c r="AP3">
-        <v>7.7812852074713</v>
+        <v>3.673928954211489</v>
       </c>
       <c r="AQ3">
-        <v>-2.281879194630873</v>
+        <v>-0.05677210056772101</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/peru/peru_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_telecom_services.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0293</v>
+        <v>-0.0404</v>
       </c>
       <c r="G2">
-        <v>0.1041413583655439</v>
+        <v>0.1551029670392012</v>
       </c>
       <c r="H2">
-        <v>0.1041413583655439</v>
+        <v>0.1551029670392012</v>
       </c>
       <c r="I2">
-        <v>-0.001909485093240669</v>
+        <v>-0.02713916561047298</v>
       </c>
       <c r="J2">
-        <v>-0.001909485093240669</v>
+        <v>-0.02713916561047298</v>
       </c>
       <c r="K2">
-        <v>-281.4</v>
+        <v>-336.7</v>
       </c>
       <c r="L2">
-        <v>-0.1553837658752071</v>
+        <v>-0.1910137856697112</v>
       </c>
       <c r="M2">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="N2">
-        <v>5.060728744939271e-06</v>
+        <v>7.73754255648406e-06</v>
       </c>
       <c r="O2">
-        <v>-7.107320540156362e-06</v>
+        <v>-1.485001485001485e-05</v>
       </c>
       <c r="P2">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="Q2">
-        <v>5.060728744939271e-06</v>
+        <v>7.73754255648406e-06</v>
       </c>
       <c r="R2">
-        <v>-7.107320540156362e-06</v>
+        <v>-1.485001485001485e-05</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>119.8</v>
+        <v>76.7</v>
       </c>
       <c r="V2">
-        <v>0.3031376518218624</v>
+        <v>0.1186939028164655</v>
       </c>
       <c r="W2">
-        <v>-0.3801161691206268</v>
+        <v>-0.6919441019317715</v>
       </c>
       <c r="X2">
-        <v>0.1735969306055751</v>
+        <v>0.124157052323791</v>
       </c>
       <c r="Y2">
-        <v>-0.5537130997262019</v>
+        <v>-0.8161011542555625</v>
       </c>
       <c r="Z2">
-        <v>1.453753942750733</v>
+        <v>1.485516025623935</v>
       </c>
       <c r="AA2">
-        <v>-0.002775921482922372</v>
+        <v>-0.04031566543641959</v>
       </c>
       <c r="AB2">
-        <v>0.08732653559018479</v>
+        <v>0.07596086113448233</v>
       </c>
       <c r="AC2">
-        <v>-0.09010245707310716</v>
+        <v>-0.1162765265709019</v>
       </c>
       <c r="AD2">
-        <v>1056.2</v>
+        <v>1195.5</v>
       </c>
       <c r="AE2">
-        <v>6.440387519294253</v>
+        <v>4.691036107903622</v>
       </c>
       <c r="AF2">
-        <v>1062.640387519294</v>
+        <v>1200.191036107904</v>
       </c>
       <c r="AG2">
-        <v>942.8403875192944</v>
+        <v>1123.491036107903</v>
       </c>
       <c r="AH2">
-        <v>0.72891408182724</v>
+        <v>0.6500199646971012</v>
       </c>
       <c r="AI2">
-        <v>0.6859105895249972</v>
+        <v>0.7694069703115352</v>
       </c>
       <c r="AJ2">
-        <v>0.7046426971216507</v>
+        <v>0.6348515154254308</v>
       </c>
       <c r="AK2">
-        <v>0.6595870634070552</v>
+        <v>0.7574823530865571</v>
       </c>
       <c r="AL2">
-        <v>78.09999999999999</v>
+        <v>112.8</v>
       </c>
       <c r="AM2">
-        <v>73.97999999999999</v>
+        <v>36.8</v>
       </c>
       <c r="AN2">
-        <v>4.115652885477147</v>
+        <v>6.130769230769231</v>
       </c>
       <c r="AO2">
-        <v>-0.05377720870678618</v>
+        <v>-0.4326241134751773</v>
       </c>
       <c r="AP2">
-        <v>3.673928954211489</v>
+        <v>5.761492492861043</v>
       </c>
       <c r="AQ2">
-        <v>-0.05677210056772101</v>
+        <v>-1.326086956521739</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0293</v>
+        <v>-0.0404</v>
       </c>
       <c r="G3">
-        <v>0.1041413583655439</v>
+        <v>0.1551029670392012</v>
       </c>
       <c r="H3">
-        <v>0.1041413583655439</v>
+        <v>0.1551029670392012</v>
       </c>
       <c r="I3">
-        <v>-0.001909485093240669</v>
+        <v>-0.02713916561047298</v>
       </c>
       <c r="J3">
-        <v>-0.001909485093240669</v>
+        <v>-0.02713916561047298</v>
       </c>
       <c r="K3">
-        <v>-281.4</v>
+        <v>-336.7</v>
       </c>
       <c r="L3">
-        <v>-0.1553837658752071</v>
+        <v>-0.1910137856697112</v>
       </c>
       <c r="M3">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="N3">
-        <v>5.060728744939271e-06</v>
+        <v>7.73754255648406e-06</v>
       </c>
       <c r="O3">
-        <v>-7.107320540156362e-06</v>
+        <v>-1.485001485001485e-05</v>
       </c>
       <c r="P3">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="Q3">
-        <v>5.060728744939271e-06</v>
+        <v>7.73754255648406e-06</v>
       </c>
       <c r="R3">
-        <v>-7.107320540156362e-06</v>
+        <v>-1.485001485001485e-05</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>119.8</v>
+        <v>76.7</v>
       </c>
       <c r="V3">
-        <v>0.3031376518218624</v>
+        <v>0.1186939028164655</v>
       </c>
       <c r="W3">
-        <v>-0.3801161691206268</v>
+        <v>-0.6919441019317715</v>
       </c>
       <c r="X3">
-        <v>0.1735969306055751</v>
+        <v>0.124157052323791</v>
       </c>
       <c r="Y3">
-        <v>-0.5537130997262019</v>
+        <v>-0.8161011542555625</v>
       </c>
       <c r="Z3">
-        <v>1.453753942750733</v>
+        <v>1.485516025623935</v>
       </c>
       <c r="AA3">
-        <v>-0.002775921482922372</v>
+        <v>-0.04031566543641959</v>
       </c>
       <c r="AB3">
-        <v>0.08732653559018479</v>
+        <v>0.07596086113448233</v>
       </c>
       <c r="AC3">
-        <v>-0.09010245707310716</v>
+        <v>-0.1162765265709019</v>
       </c>
       <c r="AD3">
-        <v>1056.2</v>
+        <v>1195.5</v>
       </c>
       <c r="AE3">
-        <v>6.440387519294253</v>
+        <v>4.691036107903622</v>
       </c>
       <c r="AF3">
-        <v>1062.640387519294</v>
+        <v>1200.191036107904</v>
       </c>
       <c r="AG3">
-        <v>942.8403875192944</v>
+        <v>1123.491036107903</v>
       </c>
       <c r="AH3">
-        <v>0.72891408182724</v>
+        <v>0.6500199646971012</v>
       </c>
       <c r="AI3">
-        <v>0.6859105895249972</v>
+        <v>0.7694069703115352</v>
       </c>
       <c r="AJ3">
-        <v>0.7046426971216507</v>
+        <v>0.6348515154254308</v>
       </c>
       <c r="AK3">
-        <v>0.6595870634070552</v>
+        <v>0.7574823530865571</v>
       </c>
       <c r="AL3">
-        <v>78.09999999999999</v>
+        <v>112.8</v>
       </c>
       <c r="AM3">
-        <v>73.97999999999999</v>
+        <v>36.8</v>
       </c>
       <c r="AN3">
-        <v>4.115652885477147</v>
+        <v>6.130769230769231</v>
       </c>
       <c r="AO3">
-        <v>-0.05377720870678618</v>
+        <v>-0.4326241134751773</v>
       </c>
       <c r="AP3">
-        <v>3.673928954211489</v>
+        <v>5.761492492861043</v>
       </c>
       <c r="AQ3">
-        <v>-0.05677210056772101</v>
+        <v>-1.326086956521739</v>
       </c>
     </row>
   </sheetData>
